--- a/Practical3/Excel Sheets/Task 7.xlsx
+++ b/Practical3/Excel Sheets/Task 7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/bhwkau001_myuct_ac_za/Documents/Y3S2/Embedded2/Prac 3/Excel Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{E83AB931-9669-4FF3-A024-D77B302D374D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2280B57E-CEB0-45A7-BB06-FFA6777E56A1}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="8_{E83AB931-9669-4FF3-A024-D77B302D374D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A71F3BA0-AD63-429D-BC54-ED42D160CB0E}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="1830" windowWidth="14610" windowHeight="15585" xr2:uid="{C3925071-ADC4-40E7-9B89-DAE59A9635E7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C3925071-ADC4-40E7-9B89-DAE59A9635E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
   <si>
     <t>Image Dimension</t>
   </si>
@@ -48,6 +48,12 @@
   </si>
   <si>
     <t>Scaling factor</t>
+  </si>
+  <si>
+    <t>Over_square</t>
+  </si>
+  <si>
+    <t>Over_cross</t>
   </si>
 </sst>
 </file>
@@ -121,14 +127,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -138,14 +138,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -481,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D56F7BE9-8876-4206-ADB9-75F8203085B2}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
@@ -489,13 +501,18 @@
     <col min="3" max="3" width="15.88671875" customWidth="1"/>
     <col min="4" max="4" width="12.88671875" customWidth="1"/>
     <col min="5" max="5" width="9.33203125" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="16.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.21875" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" s="5"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
@@ -505,12 +522,31 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
         <v>1000</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1">
         <v>128</v>
       </c>
@@ -520,10 +556,29 @@
       <c r="E2" s="1">
         <v>431106</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
+      <c r="G2" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H2" s="7"/>
+      <c r="I2" s="1">
+        <v>128</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1722</v>
+      </c>
+      <c r="K2" s="1">
+        <v>430441</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>160</v>
       </c>
@@ -533,10 +588,27 @@
       <c r="E3" s="1">
         <v>673609</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="1">
+        <v>160</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2690</v>
+      </c>
+      <c r="K3" s="1">
+        <v>672420</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>192</v>
       </c>
@@ -546,10 +618,27 @@
       <c r="E4" s="1">
         <v>970388</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="1">
+        <v>192</v>
+      </c>
+      <c r="J4" s="1">
+        <v>3871</v>
+      </c>
+      <c r="K4" s="1">
+        <v>967841</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="1">
         <v>224</v>
       </c>
@@ -559,10 +648,27 @@
       <c r="E5" s="1">
         <v>1322022</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="1">
+        <v>224</v>
+      </c>
+      <c r="J5" s="1">
+        <v>5273</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1318918</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>256</v>
       </c>
@@ -572,19 +678,41 @@
       <c r="E6">
         <v>1725458</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="1">
+        <v>256</v>
+      </c>
+      <c r="J6" s="1">
+        <v>6882</v>
+      </c>
+      <c r="K6">
+        <v>1721196</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
         <v>10000</v>
       </c>
-      <c r="B8" s="8"/>
+      <c r="B8" s="4"/>
       <c r="C8" s="1">
         <v>128</v>
       </c>
@@ -594,10 +722,29 @@
       <c r="E8" s="1">
         <v>429422</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="G8" s="4">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="1">
+        <v>128</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1725</v>
+      </c>
+      <c r="K8" s="1">
+        <v>429902</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
       <c r="C9" s="1">
         <v>160</v>
       </c>
@@ -607,10 +754,27 @@
       <c r="E9" s="1">
         <v>670837</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="1">
+        <v>160</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2691</v>
+      </c>
+      <c r="K9" s="1">
+        <v>670792</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
       <c r="C10" s="1">
         <v>192</v>
       </c>
@@ -620,10 +784,27 @@
       <c r="E10" s="1">
         <v>966620</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="1">
+        <v>192</v>
+      </c>
+      <c r="J10" s="1">
+        <v>3877</v>
+      </c>
+      <c r="K10" s="1">
+        <v>966180</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
       <c r="C11" s="1">
         <v>224</v>
       </c>
@@ -633,10 +814,27 @@
       <c r="E11" s="1">
         <v>1314908</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="1">
+        <v>224</v>
+      </c>
+      <c r="J11" s="1">
+        <v>5275</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1315182</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
       <c r="C12" s="1">
         <v>256</v>
       </c>
@@ -646,75 +844,213 @@
       <c r="E12" s="1">
         <v>1717231</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="1">
+        <v>256</v>
+      </c>
+      <c r="J12" s="1">
+        <v>6888</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1716795</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
         <v>1000000</v>
       </c>
-      <c r="B14" s="8"/>
+      <c r="B14" s="4"/>
       <c r="C14" s="1">
         <v>128</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+      <c r="D14" s="1">
+        <v>2037</v>
+      </c>
+      <c r="E14" s="1">
+        <v>429142</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="1">
+        <v>128</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1789</v>
+      </c>
+      <c r="K14" s="1">
+        <v>429346</v>
+      </c>
+      <c r="L14">
+        <v>371924</v>
+      </c>
+      <c r="M14">
+        <v>387106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
       <c r="C15" s="1">
         <v>160</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
+      <c r="D15" s="1">
+        <v>3233</v>
+      </c>
+      <c r="E15" s="1">
+        <v>670071</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="1">
+        <v>160</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2791</v>
+      </c>
+      <c r="K15" s="1">
+        <v>669809</v>
+      </c>
+      <c r="L15">
+        <v>580982</v>
+      </c>
+      <c r="M15">
+        <v>605480</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
       <c r="C16" s="1">
         <v>192</v>
       </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+      <c r="D16" s="1">
+        <v>4736</v>
+      </c>
+      <c r="E16" s="1">
+        <v>966081</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="1">
+        <v>192</v>
+      </c>
+      <c r="J16" s="1">
+        <v>4026</v>
+      </c>
+      <c r="K16" s="1">
+        <v>966227</v>
+      </c>
+      <c r="L16" s="1">
+        <v>838013</v>
+      </c>
+      <c r="M16">
+        <v>872776</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
       <c r="C17" s="1">
         <v>224</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D17" s="1">
+        <v>6347</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1315097</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="1">
+        <v>224</v>
+      </c>
+      <c r="J17" s="1">
+        <v>5479</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1315085</v>
+      </c>
+      <c r="L17" s="9">
+        <v>1140780</v>
+      </c>
+      <c r="M17" s="10">
+        <v>1188052</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="1">
         <v>256</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="D18" s="1">
+        <v>8147</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1715646</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="1">
+        <v>256</v>
+      </c>
+      <c r="J18" s="1">
+        <v>7148</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1715815</v>
+      </c>
+      <c r="L18">
+        <v>1487361</v>
+      </c>
+      <c r="M18">
+        <v>1551386</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="A14:B18"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B6"/>
     <mergeCell ref="A8:B12"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H6"/>
+    <mergeCell ref="G8:H12"/>
+    <mergeCell ref="G14:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
